--- a/Nirav Dashboard.xlsx
+++ b/Nirav Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC82F99D-90A0-48A2-904F-02748DBACC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985C5C9A-2CB4-405C-848D-8311DD185A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C68E0133-65DD-4ED2-867B-64DCA84EC161}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C68E0133-65DD-4ED2-867B-64DCA84EC161}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Data" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="51">
   <si>
     <t>Vikas</t>
   </si>
@@ -199,6 +199,12 @@
   <si>
     <t>Oct</t>
   </si>
+  <si>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t>Total Quantity</t>
+  </si>
 </sst>
 </file>
 
@@ -259,7 +265,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -285,19 +306,49 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="0" xr9:uid="{882A5CB1-5505-448C-B2BC-D6D51C191575}"/>
     <tableStyle name="Slicer Style 2" pivot="0" table="0" count="1" xr9:uid="{04DCB318-1B2E-4FDE-89E3-39474D0AD046}">
-      <tableStyleElement type="wholeTable" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Slicer Style 3" pivot="0" table="0" count="2" xr9:uid="{0B3FE3E3-2543-46FE-A74A-C94745CD7BE1}">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 4" pivot="0" table="0" count="4" xr9:uid="{0A958C9F-71D1-4ADA-A5B9-C8A2E066DB59}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="3">
+        <dxf>
+          <font>
+            <color theme="4"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <color theme="4"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <color theme="4"/>
+          </font>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 4">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="1"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -320,11 +371,47 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NIrav Pivot Table.xlsx]Pivot Table!PivotTable1</c:name>
+    <c:name>[Nirav Dashboard.xlsx]Pivot Table!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> By Region</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -403,8 +490,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -538,6 +624,44 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:dLbl>
           <c:idx val="0"/>
           <c:layout>
@@ -595,6 +719,44 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:dLbl>
           <c:idx val="0"/>
           <c:layout>
@@ -645,6 +807,44 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:dLbl>
           <c:idx val="0"/>
           <c:layout>
@@ -759,6 +959,132 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -780,6 +1106,98 @@
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-165C-404C-8EDD-D9AE8EABE714}"/>
                 </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.11249999999999989"/>
+                  <c:y val="1.5814741907261592E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="85000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.14374999999999999"/>
+                      <c:h val="6.1342592592592594E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.4581364829396377E-2"/>
+                  <c:y val="-2.3987314085739283E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.7293525809273838E-2"/>
+                  <c:y val="-4.2478127734033248E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -837,23 +1255,41 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table'!$A$2:$A$3</c:f>
+              <c:f>'Pivot Table'!$A$2:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table'!$B$2:$B$3</c:f>
+              <c:f>'Pivot Table'!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>7492569</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10716184</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8149763</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10868575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -999,11 +1435,42 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NIrav Pivot Table.xlsx]Pivot Table!PivotTable2</c:name>
+    <c:name>[Nirav Dashboard.xlsx]Pivot Table!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales By Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1082,8 +1549,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1125,6 +1591,170 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1186,6 +1816,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-401E-4A7C-9568-48A0023AF96F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1228,6 +1863,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-401E-4A7C-9568-48A0023AF96F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1270,6 +1910,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-401E-4A7C-9568-48A0023AF96F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1312,6 +1957,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-401E-4A7C-9568-48A0023AF96F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1340,16 +1990,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2058470</c:v>
+                  <c:v>7639824</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1686199</c:v>
+                  <c:v>7896972</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2656174</c:v>
+                  <c:v>12943334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1091726</c:v>
+                  <c:v>8746961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1495,11 +2145,40 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NIrav Pivot Table.xlsx]Pivot Table!PivotTable4</c:name>
+    <c:name>[Nirav Dashboard.xlsx]Pivot Table!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Over Time</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1613,7 +2292,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11590633378358482"/>
+          <c:y val="0.19988898928617529"/>
+          <c:w val="0.84701985346460829"/>
+          <c:h val="0.63625747601221982"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1714,34 +2403,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>413518</c:v>
+                  <c:v>4046530</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1524981</c:v>
+                  <c:v>3464433</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1208008</c:v>
+                  <c:v>3715672</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>804438</c:v>
+                  <c:v>3300867</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>594721</c:v>
+                  <c:v>4461095</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>996580</c:v>
+                  <c:v>3463484</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>190268</c:v>
+                  <c:v>3323401</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>574566</c:v>
+                  <c:v>4289705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>837001</c:v>
+                  <c:v>3898469</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>348488</c:v>
+                  <c:v>3263435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1985,11 +2674,47 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[NIrav Pivot Table.xlsx]Pivot Table!PivotTable3</c:name>
+    <c:name>[Nirav Dashboard.xlsx]Pivot Table!PivotTable3</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> By Product</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2098,49 +2823,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2282,28 +2965,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>619581</c:v>
+                  <c:v>3411818</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>656318</c:v>
+                  <c:v>4666911</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1963626</c:v>
+                  <c:v>4615631</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561541</c:v>
+                  <c:v>4302479</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>882968</c:v>
+                  <c:v>4820115</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1098154</c:v>
+                  <c:v>4905424</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1120178</c:v>
+                  <c:v>5906260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>590203</c:v>
+                  <c:v>4598453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4932,8 +5615,8 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-IN" sz="5400"/>
-            <a:t>Sales Dashboard</a:t>
+            <a:rPr lang="en-IN" sz="3600"/>
+            <a:t>Sales Dashboard 2026</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5015,15 +5698,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>204787</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:colOff>223837</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5052,14 +5735,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>180976</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5089,15 +5772,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>295276</xdr:colOff>
+      <xdr:colOff>200026</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>44404</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -5133,8 +5816,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="295276" y="295275"/>
-              <a:ext cx="4448174" cy="2971799"/>
+              <a:off x="200026" y="352426"/>
+              <a:ext cx="4721178" cy="1104899"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5162,6 +5845,435 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F433B5B5-4EC9-DED0-21A7-E5A93E9133E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5124449" y="1438275"/>
+          <a:ext cx="1400175" cy="1276350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD02E69-B6A0-4132-A790-855951EE7BB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6648450" y="1457325"/>
+          <a:ext cx="1504950" cy="1257301"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3A6CE0-5204-4A46-92B6-B80BF2A95D55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8286750" y="1447800"/>
+          <a:ext cx="1485900" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{925AE08B-08EB-5BE5-6B4F-0BB4874BBA4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5181600" y="1457325"/>
+          <a:ext cx="1295400" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Total Sales </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F70A2C-0C56-4F78-BE48-AA6BBCE7FDF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6762750" y="1457325"/>
+          <a:ext cx="1295400" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Total Profit</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>409576</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53571103-4738-44EE-8D48-21AEB0BD52DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8334376" y="1466850"/>
+          <a:ext cx="1419224" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1600">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Total  Ouantity</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9546,830 +10658,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A42322D-80CE-455E-BADB-CCFE7B537DE0}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="E10:F21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="301">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="11"/>
-    <field x="10"/>
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E904D42B-FB86-4CB6-B079-130D820EA302}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I10:J12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4F83D0D-EDA7-44A4-99E7-879D34DA9CA4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="M10:N15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -10390,9 +10680,9 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11123,9 +11413,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -11149,9 +11448,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4F83D0D-EDA7-44A4-99E7-879D34DA9CA4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="M10:N12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2BCC87D-DBBE-4AE4-A2BE-2B25D5190799}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -11172,9 +11471,9 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11905,9 +12204,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -11931,7 +12239,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFA8EE6D-C3F7-4156-ACEE-46079AF0F6A4}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A10:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -11954,9 +12262,9 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -12754,9 +13062,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA938F6F-CEFD-47B5-A887-F4D4255088F1}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A1:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -12777,9 +13085,9 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13510,9 +13818,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -13595,7 +13912,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52F30501-FE91-4F81-AC0D-888DFF80D51A}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="E1:F6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -13618,9 +13935,9 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14374,6 +14691,876 @@
   <dataFields count="1">
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A42322D-80CE-455E-BADB-CCFE7B537DE0}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="E10:F21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="301">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="11"/>
+    <field x="10"/>
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -14398,8 +15585,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EAEC535-0934-4EBD-9DFF-3D46D120AF0A}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="M1:N3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E904D42B-FB86-4CB6-B079-130D820EA302}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I10:J15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -14420,9 +15607,9 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15153,9 +16340,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -15180,8 +16376,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2BCC87D-DBBE-4AE4-A2BE-2B25D5190799}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I1:J3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EAEC535-0934-4EBD-9DFF-3D46D120AF0A}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="M1:N6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -15202,9 +16398,9 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15935,9 +17131,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -15977,9 +17182,9 @@
     <tabular pivotCacheId="1560770342">
       <items count="4">
         <i x="3" s="1"/>
-        <i x="0"/>
-        <i x="2"/>
-        <i x="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -15988,7 +17193,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Region" xr10:uid="{4CEC9CC0-A130-4631-AA23-D81B9771E40C}" cache="Slicer_Region" caption="Region" style="SlicerStyleDark1" rowHeight="241300"/>
+  <slicer name="Region" xr10:uid="{4CEC9CC0-A130-4631-AA23-D81B9771E40C}" cache="Slicer_Region" caption="Region" columnCount="4" style="SlicerStyleDark1" rowHeight="540000"/>
 </slicers>
 </file>
 
@@ -25973,7 +27178,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94173FB5-7618-4CD9-B25A-1F8C00ADFCAD}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -26023,7 +27228,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="5">
-        <v>2058470</v>
+        <v>7639824</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>17</v>
@@ -26040,52 +27245,106 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5">
-        <v>7492569</v>
+        <v>10716184</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="5">
-        <v>1686199</v>
+        <v>7896972</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>7492569</v>
+        <v>10716184</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>7492569</v>
+        <v>10716184</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5">
+        <v>8149763</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="5">
-        <v>2656174</v>
+        <v>12943334</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8149763</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8149763</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10868575</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="5">
-        <v>1091726</v>
+        <v>8746961</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5">
+        <v>10868575</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" s="5">
+        <v>10868575</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="5">
+        <v>37227091</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F6" s="5">
-        <v>7492569</v>
+        <v>37227091</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="5">
+        <v>37227091</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="5">
+        <v>37227091</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -26119,13 +27378,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="5">
-        <v>619581</v>
+        <v>3411818</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F11" s="5">
-        <v>413518</v>
+        <v>4046530</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>17</v>
@@ -26145,25 +27404,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>656318</v>
+        <v>4666911</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F12" s="5">
-        <v>1524981</v>
+        <v>3464433</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5">
-        <v>7492569</v>
+        <v>10716184</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N12" s="5">
-        <v>7492569</v>
+        <v>10716184</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -26171,13 +27430,25 @@
         <v>19</v>
       </c>
       <c r="B13" s="5">
-        <v>1963626</v>
+        <v>4615631</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F13" s="5">
-        <v>1208008</v>
+        <v>3715672</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="5">
+        <v>8149763</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="5">
+        <v>8149763</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -26185,13 +27456,25 @@
         <v>23</v>
       </c>
       <c r="B14" s="5">
-        <v>561541</v>
+        <v>4302479</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="5">
-        <v>804438</v>
+        <v>3300867</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <v>10868575</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="5">
+        <v>10868575</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -26199,13 +27482,25 @@
         <v>21</v>
       </c>
       <c r="B15" s="5">
-        <v>882968</v>
+        <v>4820115</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="5">
-        <v>594721</v>
+        <v>4461095</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="5">
+        <v>37227091</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="5">
+        <v>37227091</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -26213,71 +27508,84 @@
         <v>18</v>
       </c>
       <c r="B16" s="5">
-        <v>1098154</v>
+        <v>4905424</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="5">
-        <v>996580</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3463484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="5">
-        <v>1120178</v>
+        <v>5906260</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="5">
-        <v>190268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3323401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="5">
-        <v>590203</v>
+        <v>4598453</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F18" s="5">
-        <v>574566</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4289705</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="5">
-        <v>7492569</v>
+        <v>37227091</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="5">
-        <v>837001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3898469</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F20" s="5">
-        <v>348488</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3263435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="5">
-        <v>7492569</v>
+        <v>37227091</v>
+      </c>
+      <c r="J21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -26292,11 +27600,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
